--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261020.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261020.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>3,521,000</t>
+          <t>3,513,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>3,513,000</t>
+          <t>3,521,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>17,752,000</t>
+          <t>16,031,073</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>16,031,073</t>
+          <t>17,752,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>21,718,000</t>
+          <t>3,388,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,388,000</t>
+          <t>21,718,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
